--- a/docs/14-operations/templates/Teelle_New_Game_Template_v1.xlsx
+++ b/docs/14-operations/templates/Teelle_New_Game_Template_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بازی‌ها" sheetId="1" r:id="R76afc5533d9549f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بازی‌ها" sheetId="1" r:id="Rd19930aaaf894abb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -231,8 +231,8 @@
     <x:tableColumn id="7" name="موارد منع؛ با | جدا شوند"/>
     <x:tableColumn id="8" name="سطح نظارت"/>
     <x:tableColumn id="9" name="بازه سنی"/>
-    <x:tableColumn id="10" name="شروع سن به ماه"/>
-    <x:tableColumn id="11" name="پایان سن به ماه؛ غیرشامل"/>
+    <x:tableColumn id="10" name="شروع سن"/>
+    <x:tableColumn id="11" name="پایان سن"/>
     <x:tableColumn id="12" name="حداقل زمان؛ دقیقه"/>
     <x:tableColumn id="13" name="حداکثر زمان؛ دقیقه"/>
     <x:tableColumn id="14" name="زمان آماده‌سازی؛ دقیقه"/>
@@ -598,7 +598,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="6" t="str">
-        <x:v>هر بازی یک ردیف است. برای انتخاب چند گزینه، ستون‌های شماره‌دار کنار هم را پر کنید. پایان سن غیرشامل است؛ مثلاً ۲۴ یعنی تا پیش از ۲۴ماهگی.</x:v>
+        <x:v>هر بازی یک ردیف است. برای انتخاب چند گزینه، ستون‌های شماره‌دار کنار هم را پر کنید. سن، زمان، تعداد بازیکنان و همه گزینه‌های ثابت از منوی کشویی انتخاب می‌شوند.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -855,10 +855,10 @@
         <x:v>بازه سنی</x:v>
       </x:c>
       <x:c r="J4" s="26" t="str">
-        <x:v>شروع سن به ماه</x:v>
+        <x:v>شروع سن</x:v>
       </x:c>
       <x:c r="K4" s="26" t="str">
-        <x:v>پایان سن به ماه؛ غیرشامل</x:v>
+        <x:v>پایان سن</x:v>
       </x:c>
       <x:c r="L4" s="27" t="str">
         <x:v>حداقل زمان؛ دقیقه</x:v>
@@ -2984,6 +2984,12 @@
     <x:dataValidation type="list" sqref="I5:I34">
       <x:formula1>"۶ تا ۲۳ ماه,۲ تا ۳ سال,۴ تا ۶ سال,۷ تا ۹ سال,۱۰ تا ۱۲ سال"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="J5:J34">
+      <x:formula1>"۶ ماه,۷ ماه,۸ ماه,۹ ماه,۱۰ ماه,۱۱ ماه,۱۲ ماه,۱ سال,۲ سال,۳ سال,۴ سال,۵ سال,۶ سال,۷ سال,۸ سال,۹ سال,۱۰ سال,۱۱ سال,۱۲ سال"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K5:K34">
+      <x:formula1>"۶ ماه,۷ ماه,۸ ماه,۹ ماه,۱۰ ماه,۱۱ ماه,۱۲ ماه,۱ سال,۲ سال,۳ سال,۴ سال,۵ سال,۶ سال,۷ سال,۸ سال,۹ سال,۱۰ سال,۱۱ سال,۱۲ سال"</x:formula1>
+    </x:dataValidation>
     <x:dataValidation type="list" sqref="O5:O34">
       <x:formula1>"روی پا یا بغل,فضای کوچک,اتاق,فضای بزرگ,فضای باز"</x:formula1>
     </x:dataValidation>
@@ -3074,42 +3080,28 @@
     <x:dataValidation type="list" sqref="BC5:BC34">
       <x:formula1>"در انتظار,تأیید نهایی,نیاز به اصلاح,رد"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="J5:J34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="K5:K34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L5:L34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M5:M34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="N5:N34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="R5:R34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="S5:S34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="T5:T34">
-      <x:formula1>0</x:formula1>
-      <x:formula2>360</x:formula2>
+    <x:dataValidation type="list" sqref="L5:L34">
+      <x:formula1>"5,10,15,20,30,45,60,90"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M5:M34">
+      <x:formula1>"5,10,15,20,30,45,60,90,120"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N5:N34">
+      <x:formula1>"0,2,5,10,15,20,30"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="R5:R34">
+      <x:formula1>"1,2,3,4,5,6,8,10"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="S5:S34">
+      <x:formula1>"1,2,3,4,5,6,8,10"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="T5:T34">
+      <x:formula1>"0,1,2,3,4,5"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R704c54fa1bf7451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efded3611c34875"/>
   </x:tableParts>
 </x:worksheet>
 </file>